--- a/research/traditional_assets/database/data/tunisia/tunisia_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_real_estate_operations_services.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.067</v>
+        <v>0.0218</v>
       </c>
       <c r="E2">
-        <v>0.0935</v>
+        <v>-0.14</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +606,82 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>1.03</v>
+        <v>0.414</v>
       </c>
       <c r="L2">
-        <v>0.2893258426966292</v>
+        <v>0.1254545454545455</v>
       </c>
       <c r="M2">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.002556818181818182</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.008737864077669901</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.002556818181818182</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.008737864077669901</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>6.09</v>
+        <v>3.67</v>
       </c>
       <c r="V2">
-        <v>1.730113636363636</v>
+        <v>0.7943722943722943</v>
       </c>
       <c r="W2">
-        <v>0.1101604278074866</v>
+        <v>0.03869158878504673</v>
       </c>
       <c r="X2">
-        <v>1.48876488184004</v>
+        <v>1.487401051166523</v>
       </c>
       <c r="Y2">
-        <v>-1.378604454032554</v>
+        <v>-1.448709462381476</v>
       </c>
       <c r="Z2">
-        <v>0.0368797265098933</v>
+        <v>0.03845705628714602</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.1390876221140119</v>
+        <v>0.2095589946262461</v>
       </c>
       <c r="AC2">
-        <v>-0.1390876221140119</v>
+        <v>-0.2095589946262461</v>
       </c>
       <c r="AD2">
-        <v>81.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>81.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AG2">
-        <v>75.11</v>
+        <v>65.92999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.9584513692162417</v>
+        <v>0.9377526273241713</v>
       </c>
       <c r="AI2">
-        <v>0.8835690968443961</v>
+        <v>0.8743718592964824</v>
       </c>
       <c r="AJ2">
-        <v>0.9552333714867099</v>
+        <v>0.9345145287030474</v>
       </c>
       <c r="AK2">
-        <v>0.8753059084022841</v>
+        <v>0.8682997497695245</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -710,10 +707,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.067</v>
+        <v>0.0218</v>
       </c>
       <c r="E3">
-        <v>0.0935</v>
+        <v>-0.14</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,85 +725,82 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1.03</v>
+        <v>0.414</v>
       </c>
       <c r="L3">
-        <v>0.2893258426966292</v>
+        <v>0.1254545454545455</v>
       </c>
       <c r="M3">
-        <v>0.008999999999999999</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.002556818181818182</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.008737864077669901</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>0.008999999999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.002556818181818182</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.008737864077669901</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>6.09</v>
+        <v>3.67</v>
       </c>
       <c r="V3">
-        <v>1.730113636363636</v>
+        <v>0.7943722943722943</v>
       </c>
       <c r="W3">
-        <v>0.1101604278074866</v>
+        <v>0.03869158878504673</v>
       </c>
       <c r="X3">
-        <v>1.48876488184004</v>
+        <v>1.487401051166523</v>
       </c>
       <c r="Y3">
-        <v>-1.378604454032554</v>
+        <v>-1.448709462381476</v>
       </c>
       <c r="Z3">
-        <v>0.0368797265098933</v>
+        <v>0.03845705628714602</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.1390876221140119</v>
+        <v>0.2095589946262461</v>
       </c>
       <c r="AC3">
-        <v>-0.1390876221140119</v>
+        <v>-0.2095589946262461</v>
       </c>
       <c r="AD3">
-        <v>81.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>81.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="AG3">
-        <v>75.11</v>
+        <v>65.92999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.9584513692162417</v>
+        <v>0.9377526273241713</v>
       </c>
       <c r="AI3">
-        <v>0.8835690968443961</v>
+        <v>0.8743718592964824</v>
       </c>
       <c r="AJ3">
-        <v>0.9552333714867099</v>
+        <v>0.9345145287030474</v>
       </c>
       <c r="AK3">
-        <v>0.8753059084022841</v>
+        <v>0.8682997497695245</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/tunisia/tunisia_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/tunisia/tunisia_real_estate_operations_services.xlsx
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0218</v>
+        <v>0.0059</v>
       </c>
       <c r="E2">
-        <v>-0.14</v>
+        <v>0.0521</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,10 +606,10 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0.414</v>
+        <v>0.969</v>
       </c>
       <c r="L2">
-        <v>0.1254545454545455</v>
+        <v>0.2428571428571428</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -633,55 +633,55 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.67</v>
+        <v>3.26</v>
       </c>
       <c r="V2">
-        <v>0.7943722943722943</v>
+        <v>0.4429347826086956</v>
       </c>
       <c r="W2">
-        <v>0.03869158878504673</v>
+        <v>0.0969</v>
       </c>
       <c r="X2">
-        <v>1.487401051166523</v>
+        <v>0.9204583060135445</v>
       </c>
       <c r="Y2">
-        <v>-1.448709462381476</v>
+        <v>-0.8235583060135445</v>
       </c>
       <c r="Z2">
-        <v>0.03845705628714602</v>
+        <v>0.05254839984195971</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.2095589946262461</v>
+        <v>0.2030133498006149</v>
       </c>
       <c r="AC2">
-        <v>-0.2095589946262461</v>
+        <v>-0.2030133498006149</v>
       </c>
       <c r="AD2">
-        <v>69.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>69.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AG2">
-        <v>65.92999999999999</v>
+        <v>65.83999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.9377526273241713</v>
+        <v>0.9037405179178656</v>
       </c>
       <c r="AI2">
-        <v>0.8743718592964824</v>
+        <v>0.8637499999999999</v>
       </c>
       <c r="AJ2">
-        <v>0.9345145287030474</v>
+        <v>0.8994535519125683</v>
       </c>
       <c r="AK2">
-        <v>0.8682997497695245</v>
+        <v>0.8579619494396663</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0218</v>
+        <v>0.0059</v>
       </c>
       <c r="E3">
-        <v>-0.14</v>
+        <v>0.0521</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0.414</v>
+        <v>0.969</v>
       </c>
       <c r="L3">
-        <v>0.1254545454545455</v>
+        <v>0.2428571428571428</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,55 +752,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.67</v>
+        <v>3.26</v>
       </c>
       <c r="V3">
-        <v>0.7943722943722943</v>
+        <v>0.4429347826086956</v>
       </c>
       <c r="W3">
-        <v>0.03869158878504673</v>
+        <v>0.0969</v>
       </c>
       <c r="X3">
-        <v>1.487401051166523</v>
+        <v>0.9204583060135445</v>
       </c>
       <c r="Y3">
-        <v>-1.448709462381476</v>
+        <v>-0.8235583060135445</v>
       </c>
       <c r="Z3">
-        <v>0.03845705628714602</v>
+        <v>0.05254839984195971</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.2095589946262461</v>
+        <v>0.2030133498006149</v>
       </c>
       <c r="AC3">
-        <v>-0.2095589946262461</v>
+        <v>-0.2030133498006149</v>
       </c>
       <c r="AD3">
-        <v>69.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>69.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="AG3">
-        <v>65.92999999999999</v>
+        <v>65.83999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.9377526273241713</v>
+        <v>0.9037405179178656</v>
       </c>
       <c r="AI3">
-        <v>0.8743718592964824</v>
+        <v>0.8637499999999999</v>
       </c>
       <c r="AJ3">
-        <v>0.9345145287030474</v>
+        <v>0.8994535519125683</v>
       </c>
       <c r="AK3">
-        <v>0.8682997497695245</v>
+        <v>0.8579619494396663</v>
       </c>
       <c r="AL3">
         <v>0</v>
